--- a/public/assets/role_override.xlsx
+++ b/public/assets/role_override.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecali\Documents\Homework\Senior Design\Accounting-Game\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52301D83-7207-487B-9ADF-A15AE040E15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79408D9-B16C-4B81-8F49-45E954058AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1728" yWindow="1164" windowWidth="17280" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>TA (User ID)</t>
   </si>
@@ -77,13 +77,7 @@
     <t>eac0124</t>
   </si>
   <si>
-    <t>hkg0017</t>
-  </si>
-  <si>
     <t>002</t>
-  </si>
-  <si>
-    <t>001</t>
   </si>
 </sst>
 </file>
@@ -501,18 +495,12 @@
         <v>7</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>6</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/role_override.xlsx
+++ b/public/assets/role_override.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecali\Documents\Homework\Senior Design\Accounting-Game\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F79408D9-B16C-4B81-8F49-45E954058AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6CD279-72A3-4EA4-9A4E-C7D08030E820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1728" yWindow="1164" windowWidth="17280" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
-  <si>
-    <t>TA (User ID)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>Admin (User ID)</t>
   </si>
@@ -78,6 +75,24 @@
   </si>
   <si>
     <t>002</t>
+  </si>
+  <si>
+    <t>mld0076</t>
+  </si>
+  <si>
+    <t>mclelaj</t>
+  </si>
+  <si>
+    <t>hkg0017</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002,001</t>
+  </si>
+  <si>
+    <t>Professor/TA (User ID)</t>
   </si>
 </sst>
 </file>
@@ -456,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.88671875" style="1" customWidth="1"/>
@@ -467,40 +482,62 @@
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/public/assets/role_override.xlsx
+++ b/public/assets/role_override.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecali\Documents\Homework\Senior Design\Accounting-Game\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6CD279-72A3-4EA4-9A4E-C7D08030E820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D9335F-8A74-4713-8F7D-66BD9F0B2B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1728" yWindow="1164" windowWidth="17280" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
   <si>
     <t>Admin (User ID)</t>
   </si>
@@ -87,9 +87,6 @@
   </si>
   <si>
     <t>001</t>
-  </si>
-  <si>
-    <t>002,001</t>
   </si>
   <si>
     <t>Professor/TA (User ID)</t>
@@ -471,7 +468,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.88671875" style="1" customWidth="1"/>
@@ -485,7 +482,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -507,10 +504,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
@@ -518,25 +515,20 @@
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
         <v>11</v>
       </c>
     </row>

--- a/public/assets/role_override.xlsx
+++ b/public/assets/role_override.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ecali\Documents\Homework\Senior Design\Accounting-Game\public\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\School\Schoolwork\Senior Design Project (COMP 4710 - Spring 2026)\Accounting-Game\public\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5D9335F-8A74-4713-8F7D-66BD9F0B2B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DDAE90-D7A3-4A58-A0F0-F5E9545FC0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1728" yWindow="1164" windowWidth="17280" windowHeight="10008" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Admin (User ID)</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Professor/TA (User ID)</t>
+  </si>
+  <si>
+    <t>jpl0048</t>
   </si>
 </sst>
 </file>
@@ -468,16 +471,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="27" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="57.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="57.88671875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="57.88671875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="51.109375" customWidth="1"/>
+    <col min="1" max="1" width="57.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="57.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="57.85546875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="51.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="27" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -488,7 +491,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
@@ -499,7 +502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
@@ -510,7 +513,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
@@ -521,7 +524,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -530,6 +533,14 @@
       </c>
       <c r="D5" s="6" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
